--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdInvestDealQuery001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdInvestDealQuery001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14660" windowHeight="1930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14655" windowHeight="1935"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,12 +12,11 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>有效状态</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -74,6 +73,10 @@
   </si>
   <si>
     <t>是否转仓</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作资产</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -427,30 +430,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="16.453125" customWidth="1"/>
-    <col min="3" max="3" width="15.08984375" customWidth="1"/>
-    <col min="4" max="4" width="15.6328125" customWidth="1"/>
+    <col min="2" max="2" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="15.625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16.08984375" customWidth="1"/>
+    <col min="6" max="6" width="16.125" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="14.7265625" customWidth="1"/>
-    <col min="9" max="9" width="14.453125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="11" max="11" width="15.26953125" customWidth="1"/>
-    <col min="12" max="12" width="35.453125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="17.08984375" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" customWidth="1"/>
-    <col min="15" max="15" width="13.90625" customWidth="1"/>
-    <col min="16" max="16" width="15.90625" customWidth="1"/>
-    <col min="17" max="17" width="18.7265625" customWidth="1"/>
-    <col min="18" max="18" width="10.81640625" customWidth="1"/>
+    <col min="8" max="9" width="14.75" customWidth="1"/>
+    <col min="10" max="10" width="14.5" customWidth="1"/>
+    <col min="11" max="11" width="15.75" customWidth="1"/>
+    <col min="12" max="12" width="15.25" customWidth="1"/>
+    <col min="13" max="13" width="35.5" style="1" customWidth="1"/>
+    <col min="14" max="14" width="17.125" customWidth="1"/>
+    <col min="15" max="15" width="14.875" customWidth="1"/>
+    <col min="16" max="16" width="13.875" customWidth="1"/>
+    <col min="17" max="17" width="15.875" customWidth="1"/>
+    <col min="18" max="18" width="18.75" customWidth="1"/>
+    <col min="19" max="19" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -476,33 +479,36 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>13</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -516,7 +522,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -526,7 +532,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdInvestDealQuery001.xlsx
+++ b/tams-invest-parent/tams-invest-trade/src/main/resources/tpl/TrdInvestDealQuery001.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14655" windowHeight="1935"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14652" windowHeight="1932"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>有效状态</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -73,10 +73,6 @@
   </si>
   <si>
     <t>是否转仓</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>合作资产</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -430,30 +426,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="16.5" customWidth="1"/>
-    <col min="3" max="3" width="15.125" customWidth="1"/>
-    <col min="4" max="4" width="15.625" customWidth="1"/>
+    <col min="2" max="2" width="16.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="16.125" customWidth="1"/>
+    <col min="6" max="6" width="16.109375" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="9" width="14.75" customWidth="1"/>
-    <col min="10" max="10" width="14.5" customWidth="1"/>
-    <col min="11" max="11" width="15.75" customWidth="1"/>
-    <col min="12" max="12" width="15.25" customWidth="1"/>
-    <col min="13" max="13" width="35.5" style="1" customWidth="1"/>
-    <col min="14" max="14" width="17.125" customWidth="1"/>
-    <col min="15" max="15" width="14.875" customWidth="1"/>
-    <col min="16" max="16" width="13.875" customWidth="1"/>
-    <col min="17" max="17" width="15.875" customWidth="1"/>
-    <col min="18" max="18" width="18.75" customWidth="1"/>
-    <col min="19" max="19" width="10.875" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" customWidth="1"/>
+    <col min="9" max="9" width="14.44140625" customWidth="1"/>
+    <col min="10" max="10" width="15.77734375" customWidth="1"/>
+    <col min="11" max="11" width="15.21875" customWidth="1"/>
+    <col min="12" max="12" width="35.44140625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="17.109375" customWidth="1"/>
+    <col min="14" max="14" width="14.88671875" customWidth="1"/>
+    <col min="15" max="15" width="13.88671875" customWidth="1"/>
+    <col min="16" max="16" width="15.88671875" customWidth="1"/>
+    <col min="17" max="17" width="18.77734375" customWidth="1"/>
+    <col min="18" max="18" width="10.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -479,36 +475,33 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="J1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
       <c r="N1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R1" t="s">
-        <v>16</v>
-      </c>
-      <c r="S1" t="s">
         <v>17</v>
       </c>
     </row>
@@ -522,7 +515,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -532,7 +525,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
